--- a/frontend/public/gen-sticker-docs/originals/07-tdd.xlsx
+++ b/frontend/public/gen-sticker-docs/originals/07-tdd.xlsx
@@ -2,20 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visual Quality Gates" sheetId="1" r:id="R1239321c9c8d410e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visual Coverage Map" sheetId="2" r:id="R0b9b0a2b81974e3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Summary" sheetId="3" r:id="Ree661566a2dc4bab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Existing Coverage" sheetId="4" r:id="R23407d8b36de4e90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Matrix" sheetId="5" r:id="R23d19a8be58e4991"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quality Fixtures" sheetId="6" r:id="R8af701dd3ac74d72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commands" sheetId="7" r:id="Rb978b1ce0194478b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quality Gates" sheetId="8" r:id="Re09fb401cc1e40da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage Dashboard" sheetId="9" r:id="Rdf50cb11dcf643ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Matrix" sheetId="10" r:id="R99433ed494c1428c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API Matrix" sheetId="11" r:id="R01e56c4efdf34629"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integration Gaps" sheetId="12" r:id="R9ce06fcec38f4cf9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E2E Plan" sheetId="13" r:id="Ref204e1d6947402d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security Tests" sheetId="14" r:id="Rc508d01f91204a5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visual Quality Gates" sheetId="1" r:id="Rae14c21b7504496a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visual Coverage Map" sheetId="2" r:id="Rc285e8b5261f4e48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Summary" sheetId="3" r:id="R368865cb04b042d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Existing Coverage" sheetId="4" r:id="R7a0a6c36dcac454b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Matrix" sheetId="5" r:id="R531ed60cc8974b33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quality Fixtures" sheetId="6" r:id="R765088294bf2473b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commands" sheetId="7" r:id="Ra53894f140ab45e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quality Gates" sheetId="8" r:id="R4dac4351d4f74014"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage Dashboard" sheetId="9" r:id="Rf47ae15dc17445b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Matrix" sheetId="10" r:id="R3958d455d1c148f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API Matrix" sheetId="11" r:id="Rb035b59312454fc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integration Gaps" sheetId="12" r:id="Rcf6026f799004f71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E2E Plan" sheetId="13" r:id="R82c026ce5eca4cbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security Tests" sheetId="14" r:id="Rba9fc1654e9445a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Face Gate Test Matrix" sheetId="15" r:id="Rccd7bffcfe254f86"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -657,13 +658,13 @@
     <xdr:ext cx="11734800" cy="6600825"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="078f5fbc-ff91-496d-8281-67fa3d3eca10"/>
+        <xdr:cNvPr id="1" name="443187ed-d680-4f2e-a032-a169c30e6ee4"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R7a5a6434ad2a4dd1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rb8feb3e51c9942bf"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -689,13 +690,13 @@
     <xdr:ext cx="11734800" cy="6600825"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="1120d4c3-d4a7-43d2-ad51-db975378943a"/>
+        <xdr:cNvPr id="1" name="2857d7ef-a10b-4e59-8cdd-16cf26499219"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rb08c41c624704dbe"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rfb3079acd80c42b4"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -735,7 +736,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf0dc8fec0c484c83"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra2771152834a4dc1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -772,8 +773,8 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="GS0711Table" displayName="GS0711Table" ref="A6:D11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A6:D11"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="GS0711Table" displayName="GS0711Table" ref="A6:D12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A6:D12"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Scenario"/>
     <x:tableColumn id="2" name="Provider mode"/>
@@ -792,6 +793,20 @@
     <x:tableColumn id="2" name="Layer"/>
     <x:tableColumn id="3" name="Expected"/>
     <x:tableColumn id="4" name="Status"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="GS0713Table" displayName="GS0713Table" ref="A6:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A6:E13"/>
+  <x:tableColumns count="5">
+    <x:tableColumn id="1" name="Case"/>
+    <x:tableColumn id="2" name="Expected verdict"/>
+    <x:tableColumn id="3" name="UI assertion"/>
+    <x:tableColumn id="4" name="Network assertion"/>
+    <x:tableColumn id="5" name="Automation"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -1135,7 +1150,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>Từ source tests đến kiểm tra trực quan tất cả tài liệu và UI</x:v>
+        <x:v>Source tests, face-gate smoke, Office render và browser QA trước bàn giao</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -1187,7 +1202,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="16" t="str">
-        <x:v>Năm bước Backend, Frontend, Docs build, Visual QA và Browser QA</x:v>
+        <x:v>Năm bước backend, frontend, docs build, visual QA và browser QA</x:v>
       </x:c>
       <x:c r="B8" s="16"/>
       <x:c r="C8" s="16"/>
@@ -1195,7 +1210,7 @@
       <x:c r="E8" s="16"/>
       <x:c r="F8" s="16"/>
       <x:c r="I8" s="22" t="str">
-        <x:v>bên dưới là pass criteria, manual boundary và gaps</x:v>
+        <x:v>frontend gate được kiểm tra 0, 1, 2 mặt</x:v>
       </x:c>
       <x:c r="J8" s="22"/>
       <x:c r="K8" s="22"/>
@@ -1281,7 +1296,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="28" t="str">
-        <x:v>Chuỗi kiểm tra source, Office artifact và browser trước bàn giao.</x:v>
+        <x:v>callout gap nêu chưa có test tự động và direct API vẫn bypass</x:v>
       </x:c>
       <x:c r="B18" s="28"/>
       <x:c r="C18" s="28"/>
@@ -1289,7 +1304,7 @@
       <x:c r="E18" s="28"/>
       <x:c r="F18" s="28"/>
       <x:c r="I18" s="34" t="str">
-        <x:v>Chuỗi kiểm tra source, Office artifact và browser trước bàn giao.</x:v>
+        <x:v>Release gates cập nhật với QA 0/1/2 khuôn mặt, 12 Office file và giới hạn backend semantic gate chưa triển khai.</x:v>
       </x:c>
       <x:c r="J18" s="34"/>
       <x:c r="K18" s="34"/>
@@ -1375,7 +1390,7 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="43" t="str">
-        <x:v>Từ source tests đến kiểm tra trực quan tất cả tài liệu và UI
+        <x:v>Source tests, face-gate smoke, Office render và browser QA trước bàn giao
 Implemented  •  Inferred  •  Gap/Risk  •  Recommended</x:v>
       </x:c>
       <x:c r="B28" s="43"/>
@@ -1458,7 +1473,7 @@
     </x:row>
     <x:row r="42" ht="34" customHeight="1">
       <x:c r="A42" s="45" t="str">
-        <x:v>Hình GS-DOC-07 — Chuỗi quality gates trước bàn giao. Chuỗi kiểm tra source, Office artifact và browser trước bàn giao.</x:v>
+        <x:v>Hình GS-DOC-07 — Chuỗi quality gates trước bàn giao. Release gates cập nhật với QA 0/1/2 khuôn mặt, 12 Office file và giới hạn backend semantic gate chưa triển khai.</x:v>
       </x:c>
       <x:c r="B42" s="45"/>
       <x:c r="C42" s="45"/>
@@ -1476,7 +1491,7 @@
     </x:row>
     <x:row r="44" ht="42" customHeight="1">
       <x:c r="A44" s="49" t="str">
-        <x:v>Mô tả sơ đồ: Năm bước Backend, Frontend, Docs build, Visual QA và Browser QA; bên dưới là pass criteria, manual boundary và gaps.</x:v>
+        <x:v>Mô tả sơ đồ: Năm bước backend, frontend, docs build, visual QA và browser QA; frontend gate được kiểm tra 0, 1, 2 mặt; callout gap nêu chưa có test tự động và direct API vẫn bypass.</x:v>
       </x:c>
       <x:c r="B44" s="49"/>
       <x:c r="C44" s="49"/>
@@ -1494,7 +1509,7 @@
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="51" t="str">
-        <x:v>Nguồn: backend/app/tests; backend/sticker_generation/tests; frontend/package.json  •  kien_v5 @ c09e26a  •  2026-08-09</x:v>
+        <x:v>Nguồn: frontend/package.json; frontend/src/hooks/useImageUpload.ts; backend/app/tests  •  kien_v5 @ 4d23b9a  •  2026-08-10</x:v>
       </x:c>
       <x:c r="B46" s="51"/>
       <x:c r="C46" s="51"/>
@@ -1529,7 +1544,7 @@
   <x:printOptions horizontalCentered="1"/>
   <x:pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <x:pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="1"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5936a3679ead4d0d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca8d6bbc5d994b7d"/>
 </x:worksheet>
 </file>
 
@@ -1561,7 +1576,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-07  •  kien_v5 @ c09e26a  •  2026-08-09  •  75 backend tests</x:v>
+        <x:v>GS-DOC-07  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  75 backend tests</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -1673,7 +1688,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2dec0aa1abf4389"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f0c3b0da5f348b1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1709,7 +1724,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-07  •  kien_v5 @ c09e26a  •  2026-08-09  •  75 backend tests</x:v>
+        <x:v>GS-DOC-07  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  75 backend tests</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -1853,7 +1868,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2a662d607774579"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19c488c581ce4a65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1886,7 +1901,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-07  •  kien_v5 @ c09e26a  •  2026-08-09  •  75 backend tests</x:v>
+        <x:v>GS-DOC-07  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  75 backend tests</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -1993,7 +2008,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc174ac291ffa4931"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R665ca01872ef455b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2004,7 +2019,7 @@
   <x:cols>
     <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="19" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -2026,7 +2041,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-07  •  kien_v5 @ c09e26a  •  2026-08-09  •  75 backend tests</x:v>
+        <x:v>GS-DOC-07  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  75 backend tests</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -2054,73 +2069,87 @@
         <x:v>Viewport</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="21.600000381469727" hidden="0" customHeight="1">
+    <x:row r="7" ht="54" hidden="0" customHeight="1">
       <x:c r="A7" s="69" t="str">
+        <x:v>Face gate</x:v>
+      </x:c>
+      <x:c r="B7" s="69" t="str">
+        <x:v>Local MediaPipe</x:v>
+      </x:c>
+      <x:c r="C7" s="69" t="str">
+        <x:v>0 reject; 1 verified; &gt;1 reject; reject no POST</x:v>
+      </x:c>
+      <x:c r="D7" s="69" t="str">
+        <x:v>375/390/1440</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="21.600000381469727" hidden="0" customHeight="1">
+      <x:c r="A8" s="70" t="str">
         <x:v>Guest generate</x:v>
       </x:c>
-      <x:c r="B7" s="69" t="str">
+      <x:c r="B8" s="70" t="str">
         <x:v>Mock backend</x:v>
       </x:c>
-      <x:c r="C7" s="69" t="str">
+      <x:c r="C8" s="70" t="str">
         <x:v>Auth modal; no POST</x:v>
       </x:c>
-      <x:c r="D7" s="69" t="str">
+      <x:c r="D8" s="70" t="str">
         <x:v>390/1440</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="32.400001525878906" hidden="0" customHeight="1">
-      <x:c r="A8" s="70" t="str">
-        <x:v>Happy generation</x:v>
-      </x:c>
-      <x:c r="B8" s="70" t="str">
-        <x:v>Fixture job</x:v>
-      </x:c>
-      <x:c r="C8" s="70" t="str">
-        <x:v>progress → exactly 20 cards</x:v>
-      </x:c>
-      <x:c r="D8" s="70" t="str">
-        <x:v>1440</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A9" s="69" t="str">
-        <x:v>Rejected</x:v>
+        <x:v>Happy generation</x:v>
       </x:c>
       <x:c r="B9" s="69" t="str">
+        <x:v>Fixture job</x:v>
+      </x:c>
+      <x:c r="C9" s="69" t="str">
+        <x:v>progress → exactly 20 cards</x:v>
+      </x:c>
+      <x:c r="D9" s="69" t="str">
+        <x:v>1440</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A10" s="70" t="str">
+        <x:v>Rejected output</x:v>
+      </x:c>
+      <x:c r="B10" s="70" t="str">
         <x:v>Fixture raw preview</x:v>
       </x:c>
-      <x:c r="C9" s="69" t="str">
+      <x:c r="C10" s="70" t="str">
         <x:v>CTA clears state → Upload</x:v>
       </x:c>
-      <x:c r="D9" s="69" t="str">
+      <x:c r="D10" s="70" t="str">
         <x:v>390/1440</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="21.600000381469727" hidden="0" customHeight="1">
-      <x:c r="A10" s="70" t="str">
+    <x:row r="11" ht="21.600000381469727" hidden="0" customHeight="1">
+      <x:c r="A11" s="69" t="str">
         <x:v>History owner</x:v>
       </x:c>
-      <x:c r="B10" s="70" t="str">
+      <x:c r="B11" s="69" t="str">
         <x:v>Fixture API</x:v>
       </x:c>
-      <x:c r="C10" s="70" t="str">
+      <x:c r="C11" s="69" t="str">
         <x:v>open/list/delete</x:v>
       </x:c>
-      <x:c r="D10" s="70" t="str">
+      <x:c r="D11" s="69" t="str">
         <x:v>1440</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="32.400001525878906" hidden="0" customHeight="1">
-      <x:c r="A11" s="69" t="str">
+    <x:row r="12" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A12" s="70" t="str">
         <x:v>Docs hub</x:v>
       </x:c>
-      <x:c r="B11" s="69" t="str">
+      <x:c r="B12" s="70" t="str">
         <x:v>Static manifest</x:v>
       </x:c>
-      <x:c r="C11" s="69" t="str">
-        <x:v>11 files, visuals, downloads</x:v>
-      </x:c>
-      <x:c r="D11" s="69" t="str">
+      <x:c r="C12" s="70" t="str">
+        <x:v>12 files, visuals, downloads</x:v>
+      </x:c>
+      <x:c r="D12" s="70" t="str">
         <x:v>390/1440</x:v>
       </x:c>
     </x:row>
@@ -2133,7 +2162,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca2f842c5cfc4621"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9b3903a6bd9469b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2166,7 +2195,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-07  •  kien_v5 @ c09e26a  •  2026-08-09  •  75 backend tests</x:v>
+        <x:v>GS-DOC-07  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  75 backend tests</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -2287,7 +2316,204 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7896cd3a0a04db7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7db7652f84e481f"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="21" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="19" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="38" customHeight="1">
+      <x:c r="A1" s="53" t="str">
+        <x:v>07  /  Test-Driven Development</x:v>
+      </x:c>
+      <x:c r="B1" s="53"/>
+      <x:c r="C1" s="53"/>
+      <x:c r="D1" s="53"/>
+      <x:c r="E1" s="53"/>
+    </x:row>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="56" t="str">
+        <x:v>Manual evidence hiện tại và regression cases cần tự động hóa</x:v>
+      </x:c>
+      <x:c r="B2" s="56"/>
+      <x:c r="C2" s="56"/>
+      <x:c r="D2" s="56"/>
+      <x:c r="E2" s="56"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="57" t="str">
+        <x:v>GS-DOC-07  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  75 backend tests</x:v>
+      </x:c>
+      <x:c r="B3" s="57"/>
+      <x:c r="C3" s="57"/>
+      <x:c r="D3" s="57"/>
+      <x:c r="E3" s="57"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="58" t="str">
+        <x:v>AS-BUILT • Nội dung viết từ source hiện tại; bộ mẫu chỉ cung cấp cấu trúc trình bày.</x:v>
+      </x:c>
+      <x:c r="B4" s="58"/>
+      <x:c r="C4" s="58"/>
+      <x:c r="D4" s="58"/>
+      <x:c r="E4" s="58"/>
+    </x:row>
+    <x:row r="6" ht="30" customHeight="1">
+      <x:c r="A6" s="64" t="str">
+        <x:v>Case</x:v>
+      </x:c>
+      <x:c r="B6" s="64" t="str">
+        <x:v>Expected verdict</x:v>
+      </x:c>
+      <x:c r="C6" s="64" t="str">
+        <x:v>UI assertion</x:v>
+      </x:c>
+      <x:c r="D6" s="64" t="str">
+        <x:v>Network assertion</x:v>
+      </x:c>
+      <x:c r="E6" s="64" t="str">
+        <x:v>Automation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A7" s="69" t="str">
+        <x:v>0 human face</x:v>
+      </x:c>
+      <x:c r="B7" s="69" t="str">
+        <x:v>Reject</x:v>
+      </x:c>
+      <x:c r="C7" s="69" t="str">
+        <x:v>Inline no-face error; no preview</x:v>
+      </x:c>
+      <x:c r="D7" s="69" t="str">
+        <x:v>No generate POST</x:v>
+      </x:c>
+      <x:c r="E7" s="69" t="str">
+        <x:v>Manual pass; E2E gap</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A8" s="70" t="str">
+        <x:v>Exactly 1 detected face</x:v>
+      </x:c>
+      <x:c r="B8" s="70" t="str">
+        <x:v>Accept</x:v>
+      </x:c>
+      <x:c r="C8" s="70" t="str">
+        <x:v>Verified shield + preview</x:v>
+      </x:c>
+      <x:c r="D8" s="70" t="str">
+        <x:v>Generate allowed</x:v>
+      </x:c>
+      <x:c r="E8" s="70" t="str">
+        <x:v>Manual pass; E2E gap</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A9" s="69" t="str">
+        <x:v>2 detected faces</x:v>
+      </x:c>
+      <x:c r="B9" s="69" t="str">
+        <x:v>Reject</x:v>
+      </x:c>
+      <x:c r="C9" s="69" t="str">
+        <x:v>Count error; no preview</x:v>
+      </x:c>
+      <x:c r="D9" s="69" t="str">
+        <x:v>No generate POST</x:v>
+      </x:c>
+      <x:c r="E9" s="69" t="str">
+        <x:v>Manual pass; E2E gap</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A10" s="70" t="str">
+        <x:v>Worker/WASM/model error</x:v>
+      </x:c>
+      <x:c r="B10" s="70" t="str">
+        <x:v>Reject</x:v>
+      </x:c>
+      <x:c r="C10" s="70" t="str">
+        <x:v>Fail-closed error</x:v>
+      </x:c>
+      <x:c r="D10" s="70" t="str">
+        <x:v>No generate POST</x:v>
+      </x:c>
+      <x:c r="E10" s="70" t="str">
+        <x:v>Unit/E2E gap</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="21.600000381469727" hidden="0" customHeight="1">
+      <x:c r="A11" s="69" t="str">
+        <x:v>45s timeout</x:v>
+      </x:c>
+      <x:c r="B11" s="69" t="str">
+        <x:v>Reject</x:v>
+      </x:c>
+      <x:c r="C11" s="69" t="str">
+        <x:v>Worker reset</x:v>
+      </x:c>
+      <x:c r="D11" s="69" t="str">
+        <x:v>No generate POST</x:v>
+      </x:c>
+      <x:c r="E11" s="69" t="str">
+        <x:v>Unit gap</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A12" s="70" t="str">
+        <x:v>Stale request/clear</x:v>
+      </x:c>
+      <x:c r="B12" s="70" t="str">
+        <x:v>Ignore old result</x:v>
+      </x:c>
+      <x:c r="C12" s="70" t="str">
+        <x:v>Newest state only</x:v>
+      </x:c>
+      <x:c r="D12" s="70" t="str">
+        <x:v>No unintended POST</x:v>
+      </x:c>
+      <x:c r="E12" s="70" t="str">
+        <x:v>Unit gap</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A13" s="69" t="str">
+        <x:v>Direct API no-person image</x:v>
+      </x:c>
+      <x:c r="B13" s="69" t="str">
+        <x:v>Outside client gate</x:v>
+      </x:c>
+      <x:c r="C13" s="69" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="D13" s="69" t="str">
+        <x:v>Backend currently may accept</x:v>
+      </x:c>
+      <x:c r="E13" s="69" t="str">
+        <x:v>Backend gap</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:E1"/>
+    <x:mergeCell ref="A2:E2"/>
+    <x:mergeCell ref="A3:E3"/>
+    <x:mergeCell ref="A4:E4"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd443d32ad7de45c1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2335,7 +2561,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>75 backend tests được phân bổ theo module; vùng trắng được ghi rõ thay vì suy đoán</x:v>
+        <x:v>75 backend tests + manual face-gate proof; automated frontend coverage vẫn là gap</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -2387,7 +2613,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="16" t="str">
-        <x:v>Sáu nhóm test backend ở trái và ba nhóm coverage gap ở phải, gồm frontend, external integration và non-functional</x:v>
+        <x:v>Bên trái là 75 backend cases, giữa là manual browser matrix 0 mặt reject, 1 mặt pass, 2 mặt reject, bên phải là gap frontend unit/E2E và backend authoritative detector</x:v>
       </x:c>
       <x:c r="B8" s="16"/>
       <x:c r="C8" s="16"/>
@@ -2395,7 +2621,7 @@
       <x:c r="E8" s="16"/>
       <x:c r="F8" s="16"/>
       <x:c r="I8" s="22" t="str">
-        <x:v>Phân bổ 75 backend test cases và các vùng chưa được tự động hóa.</x:v>
+        <x:v>Coverage giữ nguyên 75 backend tests và bổ sung bằng chứng browser QA thủ công cho ba verdict face gate.</x:v>
       </x:c>
       <x:c r="J8" s="22"/>
       <x:c r="K8" s="22"/>
@@ -2481,7 +2707,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="28" t="str">
-        <x:v>Phân bổ 75 backend test cases và các vùng chưa được tự động hóa.</x:v>
+        <x:v>Coverage giữ nguyên 75 backend tests và bổ sung bằng chứng browser QA thủ công cho ba verdict face gate.</x:v>
       </x:c>
       <x:c r="B18" s="28"/>
       <x:c r="C18" s="28"/>
@@ -2489,7 +2715,7 @@
       <x:c r="E18" s="28"/>
       <x:c r="F18" s="28"/>
       <x:c r="I18" s="34" t="str">
-        <x:v>Phân bổ 75 backend test cases và các vùng chưa được tự động hóa.</x:v>
+        <x:v>Coverage giữ nguyên 75 backend tests và bổ sung bằng chứng browser QA thủ công cho ba verdict face gate.</x:v>
       </x:c>
       <x:c r="J18" s="34"/>
       <x:c r="K18" s="34"/>
@@ -2575,7 +2801,7 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="43" t="str">
-        <x:v>75 backend tests được phân bổ theo module; vùng trắng được ghi rõ thay vì suy đoán
+        <x:v>75 backend tests + manual face-gate proof; automated frontend coverage vẫn là gap
 Implemented  •  Inferred  •  Gap/Risk  •  Recommended</x:v>
       </x:c>
       <x:c r="B28" s="43"/>
@@ -2658,7 +2884,7 @@
     </x:row>
     <x:row r="42" ht="34" customHeight="1">
       <x:c r="A42" s="45" t="str">
-        <x:v>Hình GS-DOC-07 — Bản đồ coverage hiện tại. Phân bổ 75 backend test cases và các vùng chưa được tự động hóa.</x:v>
+        <x:v>Hình GS-DOC-07 — Bản đồ coverage hiện tại. Coverage giữ nguyên 75 backend tests và bổ sung bằng chứng browser QA thủ công cho ba verdict face gate.</x:v>
       </x:c>
       <x:c r="B42" s="45"/>
       <x:c r="C42" s="45"/>
@@ -2676,7 +2902,7 @@
     </x:row>
     <x:row r="44" ht="42" customHeight="1">
       <x:c r="A44" s="49" t="str">
-        <x:v>Mô tả sơ đồ: Sáu nhóm test backend ở trái và ba nhóm coverage gap ở phải, gồm frontend, external integration và non-functional.</x:v>
+        <x:v>Mô tả sơ đồ: Bên trái là 75 backend cases, giữa là manual browser matrix 0 mặt reject, 1 mặt pass, 2 mặt reject, bên phải là gap frontend unit/E2E và backend authoritative detector.</x:v>
       </x:c>
       <x:c r="B44" s="49"/>
       <x:c r="C44" s="49"/>
@@ -2694,7 +2920,7 @@
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="51" t="str">
-        <x:v>Nguồn: backend/app/tests; backend/sticker_generation/tests; frontend/package.json  •  kien_v5 @ c09e26a  •  2026-08-09</x:v>
+        <x:v>Nguồn: backend/app/tests; backend/sticker_generation/tests; frontend/src/services/faceDetectionService.ts  •  kien_v5 @ 4d23b9a  •  2026-08-10</x:v>
       </x:c>
       <x:c r="B46" s="51"/>
       <x:c r="C46" s="51"/>
@@ -2729,7 +2955,7 @@
   <x:printOptions horizontalCentered="1"/>
   <x:pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <x:pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="1"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43a44efe3cb344ef"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb88a527bc22b4f6d"/>
 </x:worksheet>
 </file>
 
@@ -2764,7 +2990,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-07  •  kien_v5 @ c09e26a  •  2026-08-09  •  75 backend tests</x:v>
+        <x:v>GS-DOC-07  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  75 backend tests</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -2891,7 +3117,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24ae5457e4024775"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5d8ce4bac6d4dcb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2921,7 +3147,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-07  •  kien_v5 @ c09e26a  •  2026-08-09  •  75 backend tests</x:v>
+        <x:v>GS-DOC-07  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  75 backend tests</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -3019,7 +3245,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3960118a6f8d4293"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6915f6a6bb73429f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3061,7 +3287,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-07  •  kien_v5 @ c09e26a  •  2026-08-09  •  75 backend tests</x:v>
+        <x:v>GS-DOC-07  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  75 backend tests</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -3348,7 +3574,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3db01b27dbb446b6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8337359192bf4cbe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3381,7 +3607,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-07  •  kien_v5 @ c09e26a  •  2026-08-09  •  75 backend tests</x:v>
+        <x:v>GS-DOC-07  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  75 backend tests</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -3502,7 +3728,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3170f328e607479e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re401bc8d8d424d65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3532,7 +3758,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-07  •  kien_v5 @ c09e26a  •  2026-08-09  •  75 backend tests</x:v>
+        <x:v>GS-DOC-07  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  75 backend tests</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -3619,7 +3845,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R350f77c4c51f4639"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c0ba0c6fcda40e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3649,7 +3875,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-07  •  kien_v5 @ c09e26a  •  2026-08-09  •  75 backend tests</x:v>
+        <x:v>GS-DOC-07  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  75 backend tests</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -3747,7 +3973,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3107f58cefa49de"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a1409c28ad04749"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3781,7 +4007,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-07  •  kien_v5 @ c09e26a  •  2026-08-09  •  75 backend tests</x:v>
+        <x:v>GS-DOC-07  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  75 backend tests</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -3882,9 +4108,9 @@
     <x:mergeCell ref="A4:E4"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99803f882fe646fb"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a17287d104e4979"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8465625e758a4604"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c6a3371ebf34a5c"/>
   </x:tableParts>
 </x:worksheet>
 </file>